--- a/backend/data/financials_by_company/125490.KQ.xlsx
+++ b/backend/data/financials_by_company/125490.KQ.xlsx
@@ -3621,10 +3621,8 @@
           <t>Incheon</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>21639</t>
-        </is>
+      <c r="D2" t="n">
+        <v>21639</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3893,7 +3891,7 @@
         <v>-0.5</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF2" t="n">
         <v>0.11798</v>
